--- a/2025 Redelineation Exercise of Sarawak/LAPORAN CADANGAN GPS/GPS PROPOSAL (FOR GITHUB).xlsx
+++ b/2025 Redelineation Exercise of Sarawak/LAPORAN CADANGAN GPS/GPS PROPOSAL (FOR GITHUB).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\TINDAKMALAYSIA NETWORK SERVICES PLT\SARAWAK\PBB LEAKED SLIDES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55C8892C-BC79-4F2A-AF4C-862690EB5E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC47366F-7DD1-4C42-A2A4-174E3F81F0C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="834" firstSheet="7" activeTab="9" xr2:uid="{9E38A2E5-CA71-4E09-8DA7-B7A2793F8EB6}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" tabRatio="834" firstSheet="7" activeTab="7" xr2:uid="{9E38A2E5-CA71-4E09-8DA7-B7A2793F8EB6}"/>
   </bookViews>
   <sheets>
     <sheet name="TABLE OF CONTENTS" sheetId="16" r:id="rId1"/>
@@ -27,7 +27,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'DUN ETHNIC &amp; ELECTORATE CHANGE'!$A$1:$AC$101</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'IMPACT OF DUN OUTCOME'!$A$2:$AF$102</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'MOVEMENT OF POLLING DISTRICTS'!$A$1:$R$1045</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'MOVEMENT OF POLLING DISTRICTS'!$A$1:$R$1046</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'PAR ETHNIC &amp; ELECTORATE CHANGE '!$A$1:$Y$33</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'PROPOSED DUN ALLOCATION'!$A$1:$N$118</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'PROPOSED PARLIAMENTARY SEATS'!$A$1:$G$33</definedName>
@@ -171,7 +171,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15971" uniqueCount="2499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15978" uniqueCount="2500">
   <si>
     <t>IBAN</t>
   </si>
@@ -7668,6 +7668,9 @@
   </si>
   <si>
     <t>IMPACT OF THE LEAKED PROPOSAL ON PARLIAMENT OUTCOME/ KESAN OLEH CADANGAN DIBOCORKAN TERHADAP KEPUTUSAN PARLIMEN</t>
+  </si>
+  <si>
+    <t>SUNGAI SENGKABANG</t>
   </si>
 </sst>
 </file>
@@ -8053,7 +8056,7 @@
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="1">
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -8063,30 +8066,6 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <i/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <i/>
-      </font>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border>
-        <bottom style="thin">
-          <color indexed="64"/>
-        </bottom>
-      </border>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -10617,7 +10596,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="34" spans="1:1" ht="29" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A34" s="25" t="s">
         <v>2368</v>
       </c>
@@ -22429,7 +22408,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A48CAC62-0220-410E-AE02-62F4290F0D0F}">
-  <dimension ref="A1:R1045"/>
+  <dimension ref="A1:R1046"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.81640625" bestFit="1" customWidth="1"/>
@@ -65144,11 +65123,11 @@
         <v>2456</v>
       </c>
       <c r="Q899">
-        <f t="shared" ref="Q899:Q963" si="28">MATCH(G899,K899,0)</f>
+        <f t="shared" ref="Q899:Q964" si="28">MATCH(G899,K899,0)</f>
         <v>1</v>
       </c>
       <c r="R899">
-        <f t="shared" ref="R899:R963" si="29">MATCH(E899,M899,0)</f>
+        <f t="shared" ref="R899:R964" si="29">MATCH(E899,M899,0)</f>
         <v>1</v>
       </c>
     </row>
@@ -65722,55 +65701,33 @@
       </c>
     </row>
     <row r="915" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A915" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B915" s="11" t="s">
-        <v>1910</v>
-      </c>
-      <c r="C915" s="11" t="s">
-        <v>1911</v>
-      </c>
-      <c r="D915" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="E915" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="F915" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="G915" s="11" t="s">
-        <v>73</v>
-      </c>
+      <c r="A915" s="11"/>
+      <c r="B915" s="11"/>
+      <c r="C915" s="11"/>
+      <c r="D915" s="11"/>
+      <c r="E915" s="11"/>
+      <c r="F915" s="11"/>
+      <c r="G915" s="11"/>
       <c r="I915" t="s">
-        <v>1911</v>
+        <v>2499</v>
       </c>
       <c r="K915" t="s">
-        <v>74</v>
+        <v>358</v>
       </c>
       <c r="L915" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="M915" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="N915" t="s">
-        <v>2456</v>
+        <v>2407</v>
       </c>
       <c r="O915" t="s">
-        <v>2456</v>
+        <v>2407</v>
       </c>
       <c r="P915" t="s">
-        <v>2260</v>
-      </c>
-      <c r="Q915" t="e">
-        <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R915">
-        <f t="shared" si="29"/>
-        <v>1</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="916" spans="1:18" x14ac:dyDescent="0.35">
@@ -65778,10 +65735,10 @@
         <v>82</v>
       </c>
       <c r="B916" s="11" t="s">
-        <v>1912</v>
+        <v>1910</v>
       </c>
       <c r="C916" s="11" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="D916" s="11" t="s">
         <v>338</v>
@@ -65796,7 +65753,7 @@
         <v>73</v>
       </c>
       <c r="I916" t="s">
-        <v>1913</v>
+        <v>1911</v>
       </c>
       <c r="K916" t="s">
         <v>74</v>
@@ -65830,10 +65787,10 @@
         <v>82</v>
       </c>
       <c r="B917" s="11" t="s">
-        <v>1914</v>
+        <v>1912</v>
       </c>
       <c r="C917" s="11" t="s">
-        <v>73</v>
+        <v>1913</v>
       </c>
       <c r="D917" s="11" t="s">
         <v>338</v>
@@ -65848,10 +65805,10 @@
         <v>73</v>
       </c>
       <c r="I917" t="s">
-        <v>73</v>
+        <v>1913</v>
       </c>
       <c r="K917" t="s">
-        <v>57</v>
+        <v>74</v>
       </c>
       <c r="L917" t="s">
         <v>338</v>
@@ -65860,10 +65817,13 @@
         <v>339</v>
       </c>
       <c r="N917" t="s">
-        <v>2407</v>
+        <v>2456</v>
       </c>
       <c r="O917" t="s">
         <v>2456</v>
+      </c>
+      <c r="P917" t="s">
+        <v>2260</v>
       </c>
       <c r="Q917" t="e">
         <f t="shared" si="28"/>
@@ -65879,10 +65839,10 @@
         <v>82</v>
       </c>
       <c r="B918" s="11" t="s">
-        <v>1915</v>
+        <v>1914</v>
       </c>
       <c r="C918" s="11" t="s">
-        <v>1916</v>
+        <v>73</v>
       </c>
       <c r="D918" s="11" t="s">
         <v>338</v>
@@ -65897,7 +65857,7 @@
         <v>73</v>
       </c>
       <c r="I918" t="s">
-        <v>1916</v>
+        <v>73</v>
       </c>
       <c r="K918" t="s">
         <v>57</v>
@@ -65924,41 +65884,52 @@
       </c>
     </row>
     <row r="919" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A919" s="11"/>
-      <c r="B919" s="11"/>
-      <c r="C919" s="11"/>
-      <c r="D919" s="11"/>
-      <c r="E919" s="11"/>
-      <c r="F919" s="11"/>
-      <c r="G919" s="11"/>
+      <c r="A919" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B919" s="11" t="s">
+        <v>1915</v>
+      </c>
+      <c r="C919" s="11" t="s">
+        <v>1916</v>
+      </c>
+      <c r="D919" s="11" t="s">
+        <v>338</v>
+      </c>
+      <c r="E919" s="11" t="s">
+        <v>339</v>
+      </c>
+      <c r="F919" s="11" t="s">
+        <v>343</v>
+      </c>
+      <c r="G919" s="11" t="s">
+        <v>73</v>
+      </c>
       <c r="I919" t="s">
-        <v>2220</v>
+        <v>1916</v>
       </c>
       <c r="K919" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="L919" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="M919" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="N919" t="s">
         <v>2407</v>
       </c>
       <c r="O919" t="s">
-        <v>2407</v>
-      </c>
-      <c r="P919" t="s">
-        <v>2302</v>
+        <v>2456</v>
       </c>
       <c r="Q919" t="e">
         <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
-      <c r="R919" t="e">
+      <c r="R919">
         <f t="shared" si="29"/>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
     </row>
     <row r="920" spans="1:18" x14ac:dyDescent="0.35">
@@ -65970,7 +65941,7 @@
       <c r="F920" s="11"/>
       <c r="G920" s="11"/>
       <c r="I920" t="s">
-        <v>1646</v>
+        <v>2220</v>
       </c>
       <c r="K920" t="s">
         <v>78</v>
@@ -66000,52 +65971,41 @@
       </c>
     </row>
     <row r="921" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A921" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B921" s="11" t="s">
-        <v>1917</v>
-      </c>
-      <c r="C921" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="D921" s="11" t="s">
-        <v>338</v>
-      </c>
-      <c r="E921" s="11" t="s">
-        <v>339</v>
-      </c>
-      <c r="F921" s="11" t="s">
-        <v>343</v>
-      </c>
-      <c r="G921" s="11" t="s">
-        <v>73</v>
-      </c>
+      <c r="A921" s="11"/>
+      <c r="B921" s="11"/>
+      <c r="C921" s="11"/>
+      <c r="D921" s="11"/>
+      <c r="E921" s="11"/>
+      <c r="F921" s="11"/>
+      <c r="G921" s="11"/>
       <c r="I921" t="s">
-        <v>57</v>
+        <v>1646</v>
       </c>
       <c r="K921" t="s">
-        <v>57</v>
+        <v>78</v>
       </c>
       <c r="L921" t="s">
-        <v>338</v>
+        <v>345</v>
       </c>
       <c r="M921" t="s">
-        <v>339</v>
+        <v>346</v>
       </c>
       <c r="N921" t="s">
         <v>2407</v>
       </c>
       <c r="O921" t="s">
-        <v>2456</v>
+        <v>2407</v>
+      </c>
+      <c r="P921" t="s">
+        <v>2302</v>
       </c>
       <c r="Q921" t="e">
         <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
-      <c r="R921">
+      <c r="R921" t="e">
         <f t="shared" si="29"/>
-        <v>1</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="922" spans="1:18" x14ac:dyDescent="0.35">
@@ -66053,10 +66013,10 @@
         <v>82</v>
       </c>
       <c r="B922" s="11" t="s">
-        <v>1918</v>
+        <v>1917</v>
       </c>
       <c r="C922" s="11" t="s">
-        <v>1919</v>
+        <v>57</v>
       </c>
       <c r="D922" s="11" t="s">
         <v>338</v>
@@ -66071,7 +66031,7 @@
         <v>73</v>
       </c>
       <c r="I922" t="s">
-        <v>1919</v>
+        <v>57</v>
       </c>
       <c r="K922" t="s">
         <v>57</v>
@@ -66102,44 +66062,44 @@
         <v>82</v>
       </c>
       <c r="B923" s="11" t="s">
-        <v>1920</v>
+        <v>1918</v>
       </c>
       <c r="C923" s="11" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="D923" s="11" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="E923" s="11" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="F923" s="11" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="G923" s="11" t="s">
-        <v>348</v>
+        <v>73</v>
       </c>
       <c r="I923" t="s">
-        <v>1921</v>
+        <v>1919</v>
       </c>
       <c r="K923" t="s">
-        <v>348</v>
+        <v>57</v>
       </c>
       <c r="L923" t="s">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="M923" t="s">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="N923" t="s">
-        <v>2456</v>
+        <v>2407</v>
       </c>
       <c r="O923" t="s">
         <v>2456</v>
       </c>
-      <c r="Q923">
+      <c r="Q923" t="e">
         <f t="shared" si="28"/>
-        <v>1</v>
+        <v>#N/A</v>
       </c>
       <c r="R923">
         <f t="shared" si="29"/>
@@ -66151,10 +66111,10 @@
         <v>82</v>
       </c>
       <c r="B924" s="11" t="s">
-        <v>1922</v>
+        <v>1920</v>
       </c>
       <c r="C924" s="11" t="s">
-        <v>623</v>
+        <v>1921</v>
       </c>
       <c r="D924" s="11" t="s">
         <v>345</v>
@@ -66169,7 +66129,7 @@
         <v>348</v>
       </c>
       <c r="I924" t="s">
-        <v>623</v>
+        <v>1921</v>
       </c>
       <c r="K924" t="s">
         <v>348</v>
@@ -66200,10 +66160,10 @@
         <v>82</v>
       </c>
       <c r="B925" s="11" t="s">
-        <v>1923</v>
+        <v>1922</v>
       </c>
       <c r="C925" s="11" t="s">
-        <v>1924</v>
+        <v>623</v>
       </c>
       <c r="D925" s="11" t="s">
         <v>345</v>
@@ -66218,7 +66178,7 @@
         <v>348</v>
       </c>
       <c r="I925" t="s">
-        <v>1924</v>
+        <v>623</v>
       </c>
       <c r="K925" t="s">
         <v>348</v>
@@ -66249,10 +66209,10 @@
         <v>82</v>
       </c>
       <c r="B926" s="11" t="s">
-        <v>1925</v>
+        <v>1923</v>
       </c>
       <c r="C926" s="11" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="D926" s="11" t="s">
         <v>345</v>
@@ -66267,7 +66227,7 @@
         <v>348</v>
       </c>
       <c r="I926" t="s">
-        <v>1926</v>
+        <v>1924</v>
       </c>
       <c r="K926" t="s">
         <v>348</v>
@@ -66298,10 +66258,10 @@
         <v>82</v>
       </c>
       <c r="B927" s="11" t="s">
-        <v>1927</v>
+        <v>1925</v>
       </c>
       <c r="C927" s="11" t="s">
-        <v>58</v>
+        <v>1926</v>
       </c>
       <c r="D927" s="11" t="s">
         <v>345</v>
@@ -66316,10 +66276,10 @@
         <v>348</v>
       </c>
       <c r="I927" t="s">
-        <v>58</v>
+        <v>1926</v>
       </c>
       <c r="K927" t="s">
-        <v>58</v>
+        <v>348</v>
       </c>
       <c r="L927" t="s">
         <v>345</v>
@@ -66328,64 +66288,64 @@
         <v>346</v>
       </c>
       <c r="N927" t="s">
+        <v>2456</v>
+      </c>
+      <c r="O927" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Q927">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="R927">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="928" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A928" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B928" s="11" t="s">
+        <v>1927</v>
+      </c>
+      <c r="C928" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="D928" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="E928" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="F928" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="G928" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="I928" t="s">
+        <v>58</v>
+      </c>
+      <c r="K928" t="s">
+        <v>58</v>
+      </c>
+      <c r="L928" t="s">
+        <v>345</v>
+      </c>
+      <c r="M928" t="s">
+        <v>346</v>
+      </c>
+      <c r="N928" t="s">
         <v>2407</v>
       </c>
-      <c r="O927" t="s">
-        <v>2456</v>
-      </c>
-      <c r="Q927" t="e">
+      <c r="O928" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Q928" t="e">
         <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
-      <c r="R927">
-        <f t="shared" si="29"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="928" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A928" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B928" s="11" t="s">
-        <v>1928</v>
-      </c>
-      <c r="C928" s="11" t="s">
-        <v>1929</v>
-      </c>
-      <c r="D928" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="E928" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="F928" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="G928" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="I928" t="s">
-        <v>1929</v>
-      </c>
-      <c r="K928" t="s">
-        <v>348</v>
-      </c>
-      <c r="L928" t="s">
-        <v>345</v>
-      </c>
-      <c r="M928" t="s">
-        <v>346</v>
-      </c>
-      <c r="N928" t="s">
-        <v>2456</v>
-      </c>
-      <c r="O928" t="s">
-        <v>2456</v>
-      </c>
-      <c r="Q928">
-        <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
       <c r="R928">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -66396,10 +66356,10 @@
         <v>82</v>
       </c>
       <c r="B929" s="11" t="s">
-        <v>1930</v>
+        <v>1928</v>
       </c>
       <c r="C929" s="11" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="D929" s="11" t="s">
         <v>345</v>
@@ -66414,10 +66374,10 @@
         <v>348</v>
       </c>
       <c r="I929" t="s">
-        <v>1931</v>
+        <v>1929</v>
       </c>
       <c r="K929" t="s">
-        <v>58</v>
+        <v>348</v>
       </c>
       <c r="L929" t="s">
         <v>345</v>
@@ -66426,64 +66386,64 @@
         <v>346</v>
       </c>
       <c r="N929" t="s">
+        <v>2456</v>
+      </c>
+      <c r="O929" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Q929">
+        <f t="shared" si="28"/>
+        <v>1</v>
+      </c>
+      <c r="R929">
+        <f t="shared" si="29"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="930" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A930" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B930" s="11" t="s">
+        <v>1930</v>
+      </c>
+      <c r="C930" s="11" t="s">
+        <v>1931</v>
+      </c>
+      <c r="D930" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="E930" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="F930" s="11" t="s">
+        <v>347</v>
+      </c>
+      <c r="G930" s="11" t="s">
+        <v>348</v>
+      </c>
+      <c r="I930" t="s">
+        <v>1931</v>
+      </c>
+      <c r="K930" t="s">
+        <v>58</v>
+      </c>
+      <c r="L930" t="s">
+        <v>345</v>
+      </c>
+      <c r="M930" t="s">
+        <v>346</v>
+      </c>
+      <c r="N930" t="s">
         <v>2407</v>
       </c>
-      <c r="O929" t="s">
-        <v>2456</v>
-      </c>
-      <c r="Q929" t="e">
+      <c r="O930" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Q930" t="e">
         <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
-      <c r="R929">
-        <f t="shared" si="29"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="930" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A930" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B930" s="11" t="s">
-        <v>1932</v>
-      </c>
-      <c r="C930" s="11" t="s">
-        <v>1933</v>
-      </c>
-      <c r="D930" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="E930" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="F930" s="11" t="s">
-        <v>347</v>
-      </c>
-      <c r="G930" s="11" t="s">
-        <v>348</v>
-      </c>
-      <c r="I930" t="s">
-        <v>1933</v>
-      </c>
-      <c r="K930" t="s">
-        <v>348</v>
-      </c>
-      <c r="L930" t="s">
-        <v>345</v>
-      </c>
-      <c r="M930" t="s">
-        <v>346</v>
-      </c>
-      <c r="N930" t="s">
-        <v>2456</v>
-      </c>
-      <c r="O930" t="s">
-        <v>2456</v>
-      </c>
-      <c r="Q930">
-        <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
       <c r="R930">
         <f t="shared" si="29"/>
         <v>1</v>
@@ -66494,10 +66454,10 @@
         <v>82</v>
       </c>
       <c r="B931" s="11" t="s">
-        <v>1934</v>
+        <v>1932</v>
       </c>
       <c r="C931" s="11" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="D931" s="11" t="s">
         <v>345</v>
@@ -66512,7 +66472,7 @@
         <v>348</v>
       </c>
       <c r="I931" t="s">
-        <v>1935</v>
+        <v>1933</v>
       </c>
       <c r="K931" t="s">
         <v>348</v>
@@ -66543,10 +66503,10 @@
         <v>82</v>
       </c>
       <c r="B932" s="11" t="s">
-        <v>1936</v>
+        <v>1934</v>
       </c>
       <c r="C932" s="11" t="s">
-        <v>351</v>
+        <v>1935</v>
       </c>
       <c r="D932" s="11" t="s">
         <v>345</v>
@@ -66555,16 +66515,16 @@
         <v>346</v>
       </c>
       <c r="F932" s="11" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="G932" s="11" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="I932" t="s">
-        <v>351</v>
+        <v>1935</v>
       </c>
       <c r="K932" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="L932" t="s">
         <v>345</v>
@@ -66588,15 +66548,29 @@
       </c>
     </row>
     <row r="933" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A933" s="11"/>
-      <c r="B933" s="11"/>
-      <c r="C933" s="11"/>
-      <c r="D933" s="11"/>
-      <c r="E933" s="11"/>
-      <c r="F933" s="11"/>
-      <c r="G933" s="11"/>
+      <c r="A933" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B933" s="11" t="s">
+        <v>1936</v>
+      </c>
+      <c r="C933" s="11" t="s">
+        <v>351</v>
+      </c>
+      <c r="D933" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="E933" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="F933" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="G933" s="11" t="s">
+        <v>351</v>
+      </c>
       <c r="I933" t="s">
-        <v>2216</v>
+        <v>351</v>
       </c>
       <c r="K933" t="s">
         <v>351</v>
@@ -66607,16 +66581,19 @@
       <c r="M933" t="s">
         <v>346</v>
       </c>
-      <c r="P933" t="s">
-        <v>2303</v>
-      </c>
-      <c r="Q933" t="e">
+      <c r="N933" t="s">
+        <v>2456</v>
+      </c>
+      <c r="O933" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Q933">
         <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R933" t="e">
+        <v>1</v>
+      </c>
+      <c r="R933">
         <f t="shared" si="29"/>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
     </row>
     <row r="934" spans="1:18" x14ac:dyDescent="0.35">
@@ -66628,7 +66605,7 @@
       <c r="F934" s="11"/>
       <c r="G934" s="11"/>
       <c r="I934" t="s">
-        <v>2217</v>
+        <v>2216</v>
       </c>
       <c r="K934" t="s">
         <v>351</v>
@@ -66660,7 +66637,7 @@
       <c r="F935" s="11"/>
       <c r="G935" s="11"/>
       <c r="I935" t="s">
-        <v>2218</v>
+        <v>2217</v>
       </c>
       <c r="K935" t="s">
         <v>351</v>
@@ -66692,7 +66669,7 @@
       <c r="F936" s="11"/>
       <c r="G936" s="11"/>
       <c r="I936" t="s">
-        <v>2219</v>
+        <v>2218</v>
       </c>
       <c r="K936" t="s">
         <v>351</v>
@@ -66724,22 +66701,16 @@
       <c r="F937" s="11"/>
       <c r="G937" s="11"/>
       <c r="I937" t="s">
-        <v>2224</v>
+        <v>2219</v>
       </c>
       <c r="K937" t="s">
-        <v>58</v>
+        <v>351</v>
       </c>
       <c r="L937" t="s">
         <v>345</v>
       </c>
       <c r="M937" t="s">
         <v>346</v>
-      </c>
-      <c r="N937" t="s">
-        <v>2407</v>
-      </c>
-      <c r="O937" t="s">
-        <v>2456</v>
       </c>
       <c r="P937" t="s">
         <v>2303</v>
@@ -66762,7 +66733,7 @@
       <c r="F938" s="11"/>
       <c r="G938" s="11"/>
       <c r="I938" t="s">
-        <v>2225</v>
+        <v>2224</v>
       </c>
       <c r="K938" t="s">
         <v>58</v>
@@ -66800,7 +66771,7 @@
       <c r="F939" s="11"/>
       <c r="G939" s="11"/>
       <c r="I939" t="s">
-        <v>2226</v>
+        <v>2225</v>
       </c>
       <c r="K939" t="s">
         <v>58</v>
@@ -66830,32 +66801,18 @@
       </c>
     </row>
     <row r="940" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A940" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B940" s="11" t="s">
-        <v>1937</v>
-      </c>
-      <c r="C940" s="11" t="s">
-        <v>1938</v>
-      </c>
-      <c r="D940" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="E940" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="F940" s="11" t="s">
-        <v>350</v>
-      </c>
-      <c r="G940" s="11" t="s">
-        <v>351</v>
-      </c>
+      <c r="A940" s="11"/>
+      <c r="B940" s="11"/>
+      <c r="C940" s="11"/>
+      <c r="D940" s="11"/>
+      <c r="E940" s="11"/>
+      <c r="F940" s="11"/>
+      <c r="G940" s="11"/>
       <c r="I940" t="s">
-        <v>1938</v>
+        <v>2226</v>
       </c>
       <c r="K940" t="s">
-        <v>351</v>
+        <v>58</v>
       </c>
       <c r="L940" t="s">
         <v>345</v>
@@ -66864,33 +66821,50 @@
         <v>346</v>
       </c>
       <c r="N940" t="s">
-        <v>2456</v>
+        <v>2407</v>
       </c>
       <c r="O940" t="s">
         <v>2456</v>
       </c>
-      <c r="Q940">
+      <c r="P940" t="s">
+        <v>2303</v>
+      </c>
+      <c r="Q940" t="e">
         <f t="shared" si="28"/>
-        <v>1</v>
-      </c>
-      <c r="R940">
+        <v>#N/A</v>
+      </c>
+      <c r="R940" t="e">
         <f t="shared" si="29"/>
-        <v>1</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="941" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A941" s="11"/>
-      <c r="B941" s="11"/>
-      <c r="C941" s="11"/>
-      <c r="D941" s="11"/>
-      <c r="E941" s="11"/>
-      <c r="F941" s="11"/>
-      <c r="G941" s="11"/>
+      <c r="A941" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B941" s="11" t="s">
+        <v>1937</v>
+      </c>
+      <c r="C941" s="11" t="s">
+        <v>1938</v>
+      </c>
+      <c r="D941" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="E941" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="F941" s="11" t="s">
+        <v>350</v>
+      </c>
+      <c r="G941" s="11" t="s">
+        <v>351</v>
+      </c>
       <c r="I941" t="s">
-        <v>2212</v>
+        <v>1938</v>
       </c>
       <c r="K941" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L941" t="s">
         <v>345</v>
@@ -66899,21 +66873,18 @@
         <v>346</v>
       </c>
       <c r="N941" t="s">
-        <v>2407</v>
+        <v>2456</v>
       </c>
       <c r="O941" t="s">
         <v>2456</v>
       </c>
-      <c r="P941" t="s">
-        <v>2304</v>
-      </c>
-      <c r="Q941" t="e">
+      <c r="Q941">
         <f t="shared" si="28"/>
-        <v>#N/A</v>
-      </c>
-      <c r="R941" t="e">
+        <v>1</v>
+      </c>
+      <c r="R941">
         <f t="shared" si="29"/>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
     </row>
     <row r="942" spans="1:18" x14ac:dyDescent="0.35">
@@ -66925,16 +66896,22 @@
       <c r="F942" s="11"/>
       <c r="G942" s="11"/>
       <c r="I942" t="s">
-        <v>2213</v>
+        <v>2212</v>
       </c>
       <c r="K942" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="L942" t="s">
         <v>345</v>
       </c>
       <c r="M942" t="s">
         <v>346</v>
+      </c>
+      <c r="N942" t="s">
+        <v>2407</v>
+      </c>
+      <c r="O942" t="s">
+        <v>2456</v>
       </c>
       <c r="P942" t="s">
         <v>2304</v>
@@ -66957,7 +66934,7 @@
       <c r="F943" s="11"/>
       <c r="G943" s="11"/>
       <c r="I943" t="s">
-        <v>2214</v>
+        <v>2213</v>
       </c>
       <c r="K943" t="s">
         <v>351</v>
@@ -66989,22 +66966,16 @@
       <c r="F944" s="11"/>
       <c r="G944" s="11"/>
       <c r="I944" t="s">
-        <v>2215</v>
+        <v>2214</v>
       </c>
       <c r="K944" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="L944" t="s">
         <v>345</v>
       </c>
       <c r="M944" t="s">
         <v>346</v>
-      </c>
-      <c r="N944" t="s">
-        <v>2407</v>
-      </c>
-      <c r="O944" t="s">
-        <v>2456</v>
       </c>
       <c r="P944" t="s">
         <v>2304</v>
@@ -67019,32 +66990,18 @@
       </c>
     </row>
     <row r="945" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A945" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B945" s="11" t="s">
-        <v>1939</v>
-      </c>
-      <c r="C945" s="11" t="s">
-        <v>1940</v>
-      </c>
-      <c r="D945" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="E945" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="F945" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="G945" s="11" t="s">
-        <v>77</v>
-      </c>
+      <c r="A945" s="11"/>
+      <c r="B945" s="11"/>
+      <c r="C945" s="11"/>
+      <c r="D945" s="11"/>
+      <c r="E945" s="11"/>
+      <c r="F945" s="11"/>
+      <c r="G945" s="11"/>
       <c r="I945" t="s">
-        <v>1940</v>
+        <v>2215</v>
       </c>
       <c r="K945" t="s">
-        <v>58</v>
+        <v>348</v>
       </c>
       <c r="L945" t="s">
         <v>345</v>
@@ -67057,29 +67014,46 @@
       </c>
       <c r="O945" t="s">
         <v>2456</v>
+      </c>
+      <c r="P945" t="s">
+        <v>2304</v>
       </c>
       <c r="Q945" t="e">
         <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
-      <c r="R945">
+      <c r="R945" t="e">
         <f t="shared" si="29"/>
-        <v>1</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="946" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A946" s="11"/>
-      <c r="B946" s="11"/>
-      <c r="C946" s="11"/>
-      <c r="D946" s="11"/>
-      <c r="E946" s="11"/>
-      <c r="F946" s="11"/>
-      <c r="G946" s="11"/>
+      <c r="A946" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B946" s="11" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C946" s="11" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D946" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="E946" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="F946" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="G946" s="11" t="s">
+        <v>77</v>
+      </c>
       <c r="I946" t="s">
-        <v>2223</v>
+        <v>1940</v>
       </c>
       <c r="K946" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="L946" t="s">
         <v>345</v>
@@ -67092,17 +67066,14 @@
       </c>
       <c r="O946" t="s">
         <v>2456</v>
-      </c>
-      <c r="P946" t="s">
-        <v>2305</v>
       </c>
       <c r="Q946" t="e">
         <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
-      <c r="R946" t="e">
+      <c r="R946">
         <f t="shared" si="29"/>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
     </row>
     <row r="947" spans="1:18" x14ac:dyDescent="0.35">
@@ -67114,10 +67085,10 @@
       <c r="F947" s="11"/>
       <c r="G947" s="11"/>
       <c r="I947" t="s">
-        <v>2227</v>
+        <v>2223</v>
       </c>
       <c r="K947" t="s">
-        <v>58</v>
+        <v>78</v>
       </c>
       <c r="L947" t="s">
         <v>345</v>
@@ -67152,7 +67123,7 @@
       <c r="F948" s="11"/>
       <c r="G948" s="11"/>
       <c r="I948" t="s">
-        <v>2228</v>
+        <v>2227</v>
       </c>
       <c r="K948" t="s">
         <v>58</v>
@@ -67190,7 +67161,7 @@
       <c r="F949" s="11"/>
       <c r="G949" s="11"/>
       <c r="I949" t="s">
-        <v>2229</v>
+        <v>2228</v>
       </c>
       <c r="K949" t="s">
         <v>58</v>
@@ -67228,7 +67199,7 @@
       <c r="F950" s="11"/>
       <c r="G950" s="11"/>
       <c r="I950" t="s">
-        <v>2230</v>
+        <v>2229</v>
       </c>
       <c r="K950" t="s">
         <v>58</v>
@@ -67266,7 +67237,7 @@
       <c r="F951" s="11"/>
       <c r="G951" s="11"/>
       <c r="I951" t="s">
-        <v>2231</v>
+        <v>2230</v>
       </c>
       <c r="K951" t="s">
         <v>58</v>
@@ -67304,7 +67275,7 @@
       <c r="F952" s="11"/>
       <c r="G952" s="11"/>
       <c r="I952" t="s">
-        <v>2232</v>
+        <v>2231</v>
       </c>
       <c r="K952" t="s">
         <v>58</v>
@@ -67342,10 +67313,10 @@
       <c r="F953" s="11"/>
       <c r="G953" s="11"/>
       <c r="I953" t="s">
-        <v>2233</v>
+        <v>2232</v>
       </c>
       <c r="K953" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="L953" t="s">
         <v>345</v>
@@ -67380,7 +67351,7 @@
       <c r="F954" s="11"/>
       <c r="G954" s="11"/>
       <c r="I954" t="s">
-        <v>2234</v>
+        <v>2233</v>
       </c>
       <c r="K954" t="s">
         <v>59</v>
@@ -67418,7 +67389,7 @@
       <c r="F955" s="11"/>
       <c r="G955" s="11"/>
       <c r="I955" t="s">
-        <v>2235</v>
+        <v>2234</v>
       </c>
       <c r="K955" t="s">
         <v>59</v>
@@ -67456,7 +67427,7 @@
       <c r="F956" s="11"/>
       <c r="G956" s="11"/>
       <c r="I956" t="s">
-        <v>2236</v>
+        <v>2235</v>
       </c>
       <c r="K956" t="s">
         <v>59</v>
@@ -67494,7 +67465,7 @@
       <c r="F957" s="11"/>
       <c r="G957" s="11"/>
       <c r="I957" t="s">
-        <v>2237</v>
+        <v>2236</v>
       </c>
       <c r="K957" t="s">
         <v>59</v>
@@ -67532,7 +67503,7 @@
       <c r="F958" s="11"/>
       <c r="G958" s="11"/>
       <c r="I958" t="s">
-        <v>2238</v>
+        <v>2237</v>
       </c>
       <c r="K958" t="s">
         <v>59</v>
@@ -67570,7 +67541,7 @@
       <c r="F959" s="11"/>
       <c r="G959" s="11"/>
       <c r="I959" t="s">
-        <v>2239</v>
+        <v>2238</v>
       </c>
       <c r="K959" t="s">
         <v>59</v>
@@ -67600,32 +67571,18 @@
       </c>
     </row>
     <row r="960" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A960" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B960" s="11" t="s">
-        <v>1941</v>
-      </c>
-      <c r="C960" s="11" t="s">
-        <v>1942</v>
-      </c>
-      <c r="D960" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="E960" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="F960" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="G960" s="11" t="s">
-        <v>77</v>
-      </c>
+      <c r="A960" s="11"/>
+      <c r="B960" s="11"/>
+      <c r="C960" s="11"/>
+      <c r="D960" s="11"/>
+      <c r="E960" s="11"/>
+      <c r="F960" s="11"/>
+      <c r="G960" s="11"/>
       <c r="I960" t="s">
-        <v>1942</v>
+        <v>2239</v>
       </c>
       <c r="K960" t="s">
-        <v>78</v>
+        <v>59</v>
       </c>
       <c r="L960" t="s">
         <v>345</v>
@@ -67634,36 +67591,50 @@
         <v>346</v>
       </c>
       <c r="N960" t="s">
-        <v>2456</v>
+        <v>2407</v>
       </c>
       <c r="O960" t="s">
         <v>2456</v>
       </c>
       <c r="P960" t="s">
-        <v>2262</v>
+        <v>2305</v>
       </c>
       <c r="Q960" t="e">
         <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
-      <c r="R960">
+      <c r="R960" t="e">
         <f t="shared" si="29"/>
-        <v>1</v>
+        <v>#N/A</v>
       </c>
     </row>
     <row r="961" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A961" s="11"/>
-      <c r="B961" s="11"/>
-      <c r="C961" s="11"/>
-      <c r="D961" s="11"/>
-      <c r="E961" s="11"/>
-      <c r="F961" s="11"/>
-      <c r="G961" s="11"/>
+      <c r="A961" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B961" s="11" t="s">
+        <v>1941</v>
+      </c>
+      <c r="C961" s="11" t="s">
+        <v>1942</v>
+      </c>
+      <c r="D961" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="E961" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="F961" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="G961" s="11" t="s">
+        <v>77</v>
+      </c>
       <c r="I961" t="s">
-        <v>2210</v>
+        <v>1942</v>
       </c>
       <c r="K961" t="s">
-        <v>348</v>
+        <v>78</v>
       </c>
       <c r="L961" t="s">
         <v>345</v>
@@ -67672,21 +67643,21 @@
         <v>346</v>
       </c>
       <c r="N961" t="s">
-        <v>2407</v>
+        <v>2456</v>
       </c>
       <c r="O961" t="s">
         <v>2456</v>
       </c>
       <c r="P961" t="s">
-        <v>2306</v>
+        <v>2262</v>
       </c>
       <c r="Q961" t="e">
         <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
-      <c r="R961" t="e">
+      <c r="R961">
         <f t="shared" si="29"/>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
     </row>
     <row r="962" spans="1:18" x14ac:dyDescent="0.35">
@@ -67698,7 +67669,7 @@
       <c r="F962" s="11"/>
       <c r="G962" s="11"/>
       <c r="I962" t="s">
-        <v>2211</v>
+        <v>2210</v>
       </c>
       <c r="K962" t="s">
         <v>348</v>
@@ -67736,10 +67707,10 @@
       <c r="F963" s="11"/>
       <c r="G963" s="11"/>
       <c r="I963" t="s">
-        <v>2221</v>
+        <v>2211</v>
       </c>
       <c r="K963" t="s">
-        <v>58</v>
+        <v>348</v>
       </c>
       <c r="L963" t="s">
         <v>345</v>
@@ -67774,10 +67745,10 @@
       <c r="F964" s="11"/>
       <c r="G964" s="11"/>
       <c r="I964" t="s">
-        <v>2222</v>
+        <v>2221</v>
       </c>
       <c r="K964" t="s">
-        <v>78</v>
+        <v>58</v>
       </c>
       <c r="L964" t="s">
         <v>345</v>
@@ -67785,42 +67756,34 @@
       <c r="M964" t="s">
         <v>346</v>
       </c>
+      <c r="N964" t="s">
+        <v>2407</v>
+      </c>
+      <c r="O964" t="s">
+        <v>2456</v>
+      </c>
       <c r="P964" t="s">
         <v>2306</v>
       </c>
       <c r="Q964" t="e">
-        <f t="shared" ref="Q964:Q1027" si="30">MATCH(G964,K964,0)</f>
+        <f t="shared" si="28"/>
         <v>#N/A</v>
       </c>
       <c r="R964" t="e">
-        <f t="shared" ref="R964:R1027" si="31">MATCH(E964,M964,0)</f>
+        <f t="shared" si="29"/>
         <v>#N/A</v>
       </c>
     </row>
     <row r="965" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A965" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B965" s="11" t="s">
-        <v>1943</v>
-      </c>
-      <c r="C965" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D965" s="11" t="s">
-        <v>345</v>
-      </c>
-      <c r="E965" s="11" t="s">
-        <v>346</v>
-      </c>
-      <c r="F965" s="11" t="s">
-        <v>353</v>
-      </c>
-      <c r="G965" s="11" t="s">
-        <v>77</v>
-      </c>
+      <c r="A965" s="11"/>
+      <c r="B965" s="11"/>
+      <c r="C965" s="11"/>
+      <c r="D965" s="11"/>
+      <c r="E965" s="11"/>
+      <c r="F965" s="11"/>
+      <c r="G965" s="11"/>
       <c r="I965" t="s">
-        <v>78</v>
+        <v>2222</v>
       </c>
       <c r="K965" t="s">
         <v>78</v>
@@ -67831,68 +67794,65 @@
       <c r="M965" t="s">
         <v>346</v>
       </c>
-      <c r="N965" t="s">
-        <v>2456</v>
-      </c>
-      <c r="O965" t="s">
-        <v>2456</v>
-      </c>
       <c r="P965" t="s">
+        <v>2306</v>
+      </c>
+      <c r="Q965" t="e">
+        <f t="shared" ref="Q965:Q1028" si="30">MATCH(G965,K965,0)</f>
+        <v>#N/A</v>
+      </c>
+      <c r="R965" t="e">
+        <f t="shared" ref="R965:R1028" si="31">MATCH(E965,M965,0)</f>
+        <v>#N/A</v>
+      </c>
+    </row>
+    <row r="966" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A966" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B966" s="11" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C966" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="D966" s="11" t="s">
+        <v>345</v>
+      </c>
+      <c r="E966" s="11" t="s">
+        <v>346</v>
+      </c>
+      <c r="F966" s="11" t="s">
+        <v>353</v>
+      </c>
+      <c r="G966" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="I966" t="s">
+        <v>78</v>
+      </c>
+      <c r="K966" t="s">
+        <v>78</v>
+      </c>
+      <c r="L966" t="s">
+        <v>345</v>
+      </c>
+      <c r="M966" t="s">
+        <v>346</v>
+      </c>
+      <c r="N966" t="s">
+        <v>2456</v>
+      </c>
+      <c r="O966" t="s">
+        <v>2456</v>
+      </c>
+      <c r="P966" t="s">
         <v>2262</v>
       </c>
-      <c r="Q965" t="e">
+      <c r="Q966" t="e">
         <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
-      <c r="R965">
-        <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="966" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A966" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B966" s="11" t="s">
-        <v>1944</v>
-      </c>
-      <c r="C966" s="11" t="s">
-        <v>1945</v>
-      </c>
-      <c r="D966" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="E966" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="F966" s="11" t="s">
-        <v>357</v>
-      </c>
-      <c r="G966" s="11" t="s">
-        <v>358</v>
-      </c>
-      <c r="I966" t="s">
-        <v>1945</v>
-      </c>
-      <c r="K966" t="s">
-        <v>358</v>
-      </c>
-      <c r="L966" t="s">
-        <v>355</v>
-      </c>
-      <c r="M966" t="s">
-        <v>356</v>
-      </c>
-      <c r="N966" t="s">
-        <v>2456</v>
-      </c>
-      <c r="O966" t="s">
-        <v>2456</v>
-      </c>
-      <c r="Q966">
-        <f t="shared" si="30"/>
-        <v>1</v>
-      </c>
       <c r="R966">
         <f t="shared" si="31"/>
         <v>1</v>
@@ -67903,10 +67863,10 @@
         <v>82</v>
       </c>
       <c r="B967" s="11" t="s">
-        <v>1946</v>
+        <v>1944</v>
       </c>
       <c r="C967" s="11" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="D967" s="11" t="s">
         <v>355</v>
@@ -67921,7 +67881,7 @@
         <v>358</v>
       </c>
       <c r="I967" t="s">
-        <v>1947</v>
+        <v>1945</v>
       </c>
       <c r="K967" t="s">
         <v>358</v>
@@ -67952,10 +67912,10 @@
         <v>82</v>
       </c>
       <c r="B968" s="11" t="s">
-        <v>1948</v>
+        <v>1946</v>
       </c>
       <c r="C968" s="11" t="s">
-        <v>358</v>
+        <v>1947</v>
       </c>
       <c r="D968" s="11" t="s">
         <v>355</v>
@@ -67970,7 +67930,7 @@
         <v>358</v>
       </c>
       <c r="I968" t="s">
-        <v>358</v>
+        <v>1947</v>
       </c>
       <c r="K968" t="s">
         <v>358</v>
@@ -68001,10 +67961,10 @@
         <v>82</v>
       </c>
       <c r="B969" s="11" t="s">
-        <v>1949</v>
+        <v>1948</v>
       </c>
       <c r="C969" s="11" t="s">
-        <v>1950</v>
+        <v>358</v>
       </c>
       <c r="D969" s="11" t="s">
         <v>355</v>
@@ -68019,7 +67979,7 @@
         <v>358</v>
       </c>
       <c r="I969" t="s">
-        <v>1950</v>
+        <v>358</v>
       </c>
       <c r="K969" t="s">
         <v>358</v>
@@ -68050,10 +68010,10 @@
         <v>82</v>
       </c>
       <c r="B970" s="11" t="s">
-        <v>1951</v>
+        <v>1949</v>
       </c>
       <c r="C970" s="11" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="D970" s="11" t="s">
         <v>355</v>
@@ -68068,7 +68028,7 @@
         <v>358</v>
       </c>
       <c r="I970" t="s">
-        <v>1952</v>
+        <v>1950</v>
       </c>
       <c r="K970" t="s">
         <v>358</v>
@@ -68099,10 +68059,10 @@
         <v>82</v>
       </c>
       <c r="B971" s="11" t="s">
-        <v>1953</v>
+        <v>1951</v>
       </c>
       <c r="C971" s="11" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="D971" s="11" t="s">
         <v>355</v>
@@ -68117,7 +68077,7 @@
         <v>358</v>
       </c>
       <c r="I971" t="s">
-        <v>1954</v>
+        <v>1952</v>
       </c>
       <c r="K971" t="s">
         <v>358</v>
@@ -68148,10 +68108,10 @@
         <v>82</v>
       </c>
       <c r="B972" s="11" t="s">
-        <v>1955</v>
+        <v>1953</v>
       </c>
       <c r="C972" s="11" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="D972" s="11" t="s">
         <v>355</v>
@@ -68166,10 +68126,10 @@
         <v>358</v>
       </c>
       <c r="I972" t="s">
-        <v>1956</v>
+        <v>1954</v>
       </c>
       <c r="K972" t="s">
-        <v>60</v>
+        <v>358</v>
       </c>
       <c r="L972" t="s">
         <v>355</v>
@@ -68178,64 +68138,64 @@
         <v>356</v>
       </c>
       <c r="N972" t="s">
+        <v>2456</v>
+      </c>
+      <c r="O972" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Q972">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="R972">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="973" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A973" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B973" s="11" t="s">
+        <v>1955</v>
+      </c>
+      <c r="C973" s="11" t="s">
+        <v>1956</v>
+      </c>
+      <c r="D973" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="E973" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="F973" s="11" t="s">
+        <v>357</v>
+      </c>
+      <c r="G973" s="11" t="s">
+        <v>358</v>
+      </c>
+      <c r="I973" t="s">
+        <v>1956</v>
+      </c>
+      <c r="K973" t="s">
+        <v>60</v>
+      </c>
+      <c r="L973" t="s">
+        <v>355</v>
+      </c>
+      <c r="M973" t="s">
+        <v>356</v>
+      </c>
+      <c r="N973" t="s">
         <v>2407</v>
       </c>
-      <c r="O972" t="s">
-        <v>2456</v>
-      </c>
-      <c r="Q972" t="e">
+      <c r="O973" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Q973" t="e">
         <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
-      <c r="R972">
-        <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="973" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A973" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B973" s="11" t="s">
-        <v>1957</v>
-      </c>
-      <c r="C973" s="11" t="s">
-        <v>1958</v>
-      </c>
-      <c r="D973" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="E973" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="F973" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="G973" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="I973" t="s">
-        <v>1958</v>
-      </c>
-      <c r="K973" t="s">
-        <v>361</v>
-      </c>
-      <c r="L973" t="s">
-        <v>355</v>
-      </c>
-      <c r="M973" t="s">
-        <v>356</v>
-      </c>
-      <c r="N973" t="s">
-        <v>2456</v>
-      </c>
-      <c r="O973" t="s">
-        <v>2456</v>
-      </c>
-      <c r="Q973">
-        <f t="shared" si="30"/>
-        <v>1</v>
-      </c>
       <c r="R973">
         <f t="shared" si="31"/>
         <v>1</v>
@@ -68246,10 +68206,10 @@
         <v>82</v>
       </c>
       <c r="B974" s="11" t="s">
-        <v>1959</v>
+        <v>1957</v>
       </c>
       <c r="C974" s="11" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="D974" s="11" t="s">
         <v>355</v>
@@ -68264,10 +68224,10 @@
         <v>361</v>
       </c>
       <c r="I974" t="s">
-        <v>1960</v>
+        <v>1958</v>
       </c>
       <c r="K974" t="s">
-        <v>60</v>
+        <v>361</v>
       </c>
       <c r="L974" t="s">
         <v>355</v>
@@ -68276,64 +68236,64 @@
         <v>356</v>
       </c>
       <c r="N974" t="s">
+        <v>2456</v>
+      </c>
+      <c r="O974" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Q974">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="R974">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="975" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A975" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B975" s="11" t="s">
+        <v>1959</v>
+      </c>
+      <c r="C975" s="11" t="s">
+        <v>1960</v>
+      </c>
+      <c r="D975" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="E975" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="F975" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="G975" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="I975" t="s">
+        <v>1960</v>
+      </c>
+      <c r="K975" t="s">
+        <v>60</v>
+      </c>
+      <c r="L975" t="s">
+        <v>355</v>
+      </c>
+      <c r="M975" t="s">
+        <v>356</v>
+      </c>
+      <c r="N975" t="s">
         <v>2407</v>
       </c>
-      <c r="O974" t="s">
-        <v>2456</v>
-      </c>
-      <c r="Q974" t="e">
+      <c r="O975" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Q975" t="e">
         <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
-      <c r="R974">
-        <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="975" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A975" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B975" s="11" t="s">
-        <v>1961</v>
-      </c>
-      <c r="C975" s="11" t="s">
-        <v>1962</v>
-      </c>
-      <c r="D975" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="E975" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="F975" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="G975" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="I975" t="s">
-        <v>1962</v>
-      </c>
-      <c r="K975" t="s">
-        <v>361</v>
-      </c>
-      <c r="L975" t="s">
-        <v>355</v>
-      </c>
-      <c r="M975" t="s">
-        <v>356</v>
-      </c>
-      <c r="N975" t="s">
-        <v>2456</v>
-      </c>
-      <c r="O975" t="s">
-        <v>2456</v>
-      </c>
-      <c r="Q975">
-        <f t="shared" si="30"/>
-        <v>1</v>
-      </c>
       <c r="R975">
         <f t="shared" si="31"/>
         <v>1</v>
@@ -68344,10 +68304,10 @@
         <v>82</v>
       </c>
       <c r="B976" s="11" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="C976" s="11" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="D976" s="11" t="s">
         <v>355</v>
@@ -68362,10 +68322,10 @@
         <v>361</v>
       </c>
       <c r="I976" t="s">
-        <v>1964</v>
+        <v>1962</v>
       </c>
       <c r="K976" t="s">
-        <v>60</v>
+        <v>361</v>
       </c>
       <c r="L976" t="s">
         <v>355</v>
@@ -68374,64 +68334,64 @@
         <v>356</v>
       </c>
       <c r="N976" t="s">
+        <v>2456</v>
+      </c>
+      <c r="O976" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Q976">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="R976">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="977" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A977" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B977" s="11" t="s">
+        <v>1963</v>
+      </c>
+      <c r="C977" s="11" t="s">
+        <v>1964</v>
+      </c>
+      <c r="D977" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="E977" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="F977" s="11" t="s">
+        <v>360</v>
+      </c>
+      <c r="G977" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="I977" t="s">
+        <v>1964</v>
+      </c>
+      <c r="K977" t="s">
+        <v>60</v>
+      </c>
+      <c r="L977" t="s">
+        <v>355</v>
+      </c>
+      <c r="M977" t="s">
+        <v>356</v>
+      </c>
+      <c r="N977" t="s">
         <v>2407</v>
       </c>
-      <c r="O976" t="s">
-        <v>2456</v>
-      </c>
-      <c r="Q976" t="e">
+      <c r="O977" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Q977" t="e">
         <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
-      <c r="R976">
-        <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="977" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A977" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B977" s="11" t="s">
-        <v>1965</v>
-      </c>
-      <c r="C977" s="11" t="s">
-        <v>1966</v>
-      </c>
-      <c r="D977" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="E977" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="F977" s="11" t="s">
-        <v>360</v>
-      </c>
-      <c r="G977" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="I977" t="s">
-        <v>1966</v>
-      </c>
-      <c r="K977" t="s">
-        <v>361</v>
-      </c>
-      <c r="L977" t="s">
-        <v>355</v>
-      </c>
-      <c r="M977" t="s">
-        <v>356</v>
-      </c>
-      <c r="N977" t="s">
-        <v>2456</v>
-      </c>
-      <c r="O977" t="s">
-        <v>2456</v>
-      </c>
-      <c r="Q977">
-        <f t="shared" si="30"/>
-        <v>1</v>
-      </c>
       <c r="R977">
         <f t="shared" si="31"/>
         <v>1</v>
@@ -68442,10 +68402,10 @@
         <v>82</v>
       </c>
       <c r="B978" s="11" t="s">
-        <v>1967</v>
+        <v>1965</v>
       </c>
       <c r="C978" s="11" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="D978" s="11" t="s">
         <v>355</v>
@@ -68460,7 +68420,7 @@
         <v>361</v>
       </c>
       <c r="I978" t="s">
-        <v>1968</v>
+        <v>1966</v>
       </c>
       <c r="K978" t="s">
         <v>361</v>
@@ -68491,10 +68451,10 @@
         <v>82</v>
       </c>
       <c r="B979" s="11" t="s">
-        <v>1969</v>
+        <v>1967</v>
       </c>
       <c r="C979" s="11" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="D979" s="11" t="s">
         <v>355</v>
@@ -68503,16 +68463,16 @@
         <v>356</v>
       </c>
       <c r="F979" s="11" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="G979" s="11" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="I979" t="s">
-        <v>1970</v>
+        <v>1968</v>
       </c>
       <c r="K979" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="L979" t="s">
         <v>355</v>
@@ -68540,10 +68500,10 @@
         <v>82</v>
       </c>
       <c r="B980" s="11" t="s">
-        <v>1971</v>
+        <v>1969</v>
       </c>
       <c r="C980" s="11" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="D980" s="11" t="s">
         <v>355</v>
@@ -68558,7 +68518,7 @@
         <v>364</v>
       </c>
       <c r="I980" t="s">
-        <v>1972</v>
+        <v>1970</v>
       </c>
       <c r="K980" t="s">
         <v>364</v>
@@ -68589,10 +68549,10 @@
         <v>82</v>
       </c>
       <c r="B981" s="11" t="s">
-        <v>1973</v>
+        <v>1971</v>
       </c>
       <c r="C981" s="11" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="D981" s="11" t="s">
         <v>355</v>
@@ -68607,10 +68567,10 @@
         <v>364</v>
       </c>
       <c r="I981" t="s">
-        <v>1974</v>
+        <v>1972</v>
       </c>
       <c r="K981" t="s">
-        <v>60</v>
+        <v>364</v>
       </c>
       <c r="L981" t="s">
         <v>355</v>
@@ -68619,64 +68579,64 @@
         <v>356</v>
       </c>
       <c r="N981" t="s">
+        <v>2456</v>
+      </c>
+      <c r="O981" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Q981">
+        <f t="shared" si="30"/>
+        <v>1</v>
+      </c>
+      <c r="R981">
+        <f t="shared" si="31"/>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="982" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A982" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B982" s="11" t="s">
+        <v>1973</v>
+      </c>
+      <c r="C982" s="11" t="s">
+        <v>1974</v>
+      </c>
+      <c r="D982" s="11" t="s">
+        <v>355</v>
+      </c>
+      <c r="E982" s="11" t="s">
+        <v>356</v>
+      </c>
+      <c r="F982" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="G982" s="11" t="s">
+        <v>364</v>
+      </c>
+      <c r="I982" t="s">
+        <v>1974</v>
+      </c>
+      <c r="K982" t="s">
+        <v>60</v>
+      </c>
+      <c r="L982" t="s">
+        <v>355</v>
+      </c>
+      <c r="M982" t="s">
+        <v>356</v>
+      </c>
+      <c r="N982" t="s">
         <v>2407</v>
       </c>
-      <c r="O981" t="s">
-        <v>2456</v>
-      </c>
-      <c r="Q981" t="e">
+      <c r="O982" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Q982" t="e">
         <f t="shared" si="30"/>
         <v>#N/A</v>
       </c>
-      <c r="R981">
-        <f t="shared" si="31"/>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="982" spans="1:18" x14ac:dyDescent="0.35">
-      <c r="A982" s="11" t="s">
-        <v>82</v>
-      </c>
-      <c r="B982" s="11" t="s">
-        <v>1975</v>
-      </c>
-      <c r="C982" s="11" t="s">
-        <v>1976</v>
-      </c>
-      <c r="D982" s="11" t="s">
-        <v>355</v>
-      </c>
-      <c r="E982" s="11" t="s">
-        <v>356</v>
-      </c>
-      <c r="F982" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="G982" s="11" t="s">
-        <v>364</v>
-      </c>
-      <c r="I982" t="s">
-        <v>1976</v>
-      </c>
-      <c r="K982" t="s">
-        <v>364</v>
-      </c>
-      <c r="L982" t="s">
-        <v>355</v>
-      </c>
-      <c r="M982" t="s">
-        <v>356</v>
-      </c>
-      <c r="N982" t="s">
-        <v>2456</v>
-      </c>
-      <c r="O982" t="s">
-        <v>2456</v>
-      </c>
-      <c r="Q982">
-        <f t="shared" si="30"/>
-        <v>1</v>
-      </c>
       <c r="R982">
         <f t="shared" si="31"/>
         <v>1</v>
@@ -68687,10 +68647,10 @@
         <v>82</v>
       </c>
       <c r="B983" s="11" t="s">
-        <v>1977</v>
+        <v>1975</v>
       </c>
       <c r="C983" s="11" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="D983" s="11" t="s">
         <v>355</v>
@@ -68705,7 +68665,7 @@
         <v>364</v>
       </c>
       <c r="I983" t="s">
-        <v>1978</v>
+        <v>1976</v>
       </c>
       <c r="K983" t="s">
         <v>364</v>
@@ -68736,10 +68696,10 @@
         <v>82</v>
       </c>
       <c r="B984" s="11" t="s">
-        <v>1979</v>
+        <v>1977</v>
       </c>
       <c r="C984" s="11" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="D984" s="11" t="s">
         <v>355</v>
@@ -68754,7 +68714,7 @@
         <v>364</v>
       </c>
       <c r="I984" t="s">
-        <v>1980</v>
+        <v>1978</v>
       </c>
       <c r="K984" t="s">
         <v>364</v>
@@ -68785,10 +68745,10 @@
         <v>82</v>
       </c>
       <c r="B985" s="11" t="s">
-        <v>1981</v>
+        <v>1979</v>
       </c>
       <c r="C985" s="11" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="D985" s="11" t="s">
         <v>355</v>
@@ -68803,7 +68763,7 @@
         <v>364</v>
       </c>
       <c r="I985" t="s">
-        <v>1982</v>
+        <v>1980</v>
       </c>
       <c r="K985" t="s">
         <v>364</v>
@@ -68834,10 +68794,10 @@
         <v>82</v>
       </c>
       <c r="B986" s="11" t="s">
-        <v>1983</v>
+        <v>1981</v>
       </c>
       <c r="C986" s="11" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="D986" s="11" t="s">
         <v>355</v>
@@ -68852,7 +68812,7 @@
         <v>364</v>
       </c>
       <c r="I986" t="s">
-        <v>1984</v>
+        <v>1982</v>
       </c>
       <c r="K986" t="s">
         <v>364</v>
@@ -68883,10 +68843,10 @@
         <v>82</v>
       </c>
       <c r="B987" s="11" t="s">
-        <v>1985</v>
+        <v>1983</v>
       </c>
       <c r="C987" s="11" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="D987" s="11" t="s">
         <v>355</v>
@@ -68901,7 +68861,7 @@
         <v>364</v>
       </c>
       <c r="I987" t="s">
-        <v>1986</v>
+        <v>1984</v>
       </c>
       <c r="K987" t="s">
         <v>364</v>
@@ -68932,10 +68892,10 @@
         <v>82</v>
       </c>
       <c r="B988" s="11" t="s">
-        <v>1987</v>
+        <v>1985</v>
       </c>
       <c r="C988" s="11" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="D988" s="11" t="s">
         <v>355</v>
@@ -68950,7 +68910,7 @@
         <v>364</v>
       </c>
       <c r="I988" t="s">
-        <v>1988</v>
+        <v>1986</v>
       </c>
       <c r="K988" t="s">
         <v>364</v>
@@ -68981,34 +68941,34 @@
         <v>82</v>
       </c>
       <c r="B989" s="11" t="s">
-        <v>1989</v>
+        <v>1987</v>
       </c>
       <c r="C989" s="11" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="D989" s="11" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="E989" s="11" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="F989" s="11" t="s">
-        <v>368</v>
+        <v>363</v>
       </c>
       <c r="G989" s="11" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="I989" t="s">
-        <v>1990</v>
+        <v>1988</v>
       </c>
       <c r="K989" t="s">
-        <v>369</v>
+        <v>364</v>
       </c>
       <c r="L989" t="s">
-        <v>366</v>
+        <v>355</v>
       </c>
       <c r="M989" t="s">
-        <v>367</v>
+        <v>356</v>
       </c>
       <c r="N989" t="s">
         <v>2456</v>
@@ -69030,10 +68990,10 @@
         <v>82</v>
       </c>
       <c r="B990" s="11" t="s">
-        <v>1991</v>
+        <v>1989</v>
       </c>
       <c r="C990" s="11" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="D990" s="11" t="s">
         <v>366</v>
@@ -69048,7 +69008,7 @@
         <v>369</v>
       </c>
       <c r="I990" t="s">
-        <v>1992</v>
+        <v>1990</v>
       </c>
       <c r="K990" t="s">
         <v>369</v>
@@ -69079,10 +69039,10 @@
         <v>82</v>
       </c>
       <c r="B991" s="11" t="s">
-        <v>1993</v>
+        <v>1991</v>
       </c>
       <c r="C991" s="11" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="D991" s="11" t="s">
         <v>366</v>
@@ -69097,7 +69057,7 @@
         <v>369</v>
       </c>
       <c r="I991" t="s">
-        <v>1994</v>
+        <v>1992</v>
       </c>
       <c r="K991" t="s">
         <v>369</v>
@@ -69128,10 +69088,10 @@
         <v>82</v>
       </c>
       <c r="B992" s="11" t="s">
-        <v>1995</v>
+        <v>1993</v>
       </c>
       <c r="C992" s="11" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="D992" s="11" t="s">
         <v>366</v>
@@ -69146,7 +69106,7 @@
         <v>369</v>
       </c>
       <c r="I992" t="s">
-        <v>1996</v>
+        <v>1994</v>
       </c>
       <c r="K992" t="s">
         <v>369</v>
@@ -69177,10 +69137,10 @@
         <v>82</v>
       </c>
       <c r="B993" s="11" t="s">
-        <v>1997</v>
+        <v>1995</v>
       </c>
       <c r="C993" s="11" t="s">
-        <v>367</v>
+        <v>1996</v>
       </c>
       <c r="D993" s="11" t="s">
         <v>366</v>
@@ -69195,7 +69155,7 @@
         <v>369</v>
       </c>
       <c r="I993" t="s">
-        <v>367</v>
+        <v>1996</v>
       </c>
       <c r="K993" t="s">
         <v>369</v>
@@ -69226,10 +69186,10 @@
         <v>82</v>
       </c>
       <c r="B994" s="11" t="s">
-        <v>1998</v>
+        <v>1997</v>
       </c>
       <c r="C994" s="11" t="s">
-        <v>1999</v>
+        <v>367</v>
       </c>
       <c r="D994" s="11" t="s">
         <v>366</v>
@@ -69244,7 +69204,7 @@
         <v>369</v>
       </c>
       <c r="I994" t="s">
-        <v>1999</v>
+        <v>367</v>
       </c>
       <c r="K994" t="s">
         <v>369</v>
@@ -69275,10 +69235,10 @@
         <v>82</v>
       </c>
       <c r="B995" s="11" t="s">
-        <v>2000</v>
+        <v>1998</v>
       </c>
       <c r="C995" s="11" t="s">
-        <v>369</v>
+        <v>1999</v>
       </c>
       <c r="D995" s="11" t="s">
         <v>366</v>
@@ -69293,7 +69253,7 @@
         <v>369</v>
       </c>
       <c r="I995" t="s">
-        <v>369</v>
+        <v>1999</v>
       </c>
       <c r="K995" t="s">
         <v>369</v>
@@ -69324,10 +69284,10 @@
         <v>82</v>
       </c>
       <c r="B996" s="11" t="s">
-        <v>2001</v>
+        <v>2000</v>
       </c>
       <c r="C996" s="11" t="s">
-        <v>2002</v>
+        <v>369</v>
       </c>
       <c r="D996" s="11" t="s">
         <v>366</v>
@@ -69342,7 +69302,7 @@
         <v>369</v>
       </c>
       <c r="I996" t="s">
-        <v>2002</v>
+        <v>369</v>
       </c>
       <c r="K996" t="s">
         <v>369</v>
@@ -69373,10 +69333,10 @@
         <v>82</v>
       </c>
       <c r="B997" s="11" t="s">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C997" s="11" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="D997" s="11" t="s">
         <v>366</v>
@@ -69391,7 +69351,7 @@
         <v>369</v>
       </c>
       <c r="I997" t="s">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="K997" t="s">
         <v>369</v>
@@ -69422,10 +69382,10 @@
         <v>82</v>
       </c>
       <c r="B998" s="11" t="s">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C998" s="11" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="D998" s="11" t="s">
         <v>366</v>
@@ -69440,7 +69400,7 @@
         <v>369</v>
       </c>
       <c r="I998" t="s">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="K998" t="s">
         <v>369</v>
@@ -69471,10 +69431,10 @@
         <v>82</v>
       </c>
       <c r="B999" s="11" t="s">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="C999" s="11" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="D999" s="11" t="s">
         <v>366</v>
@@ -69483,16 +69443,16 @@
         <v>367</v>
       </c>
       <c r="F999" s="11" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="G999" s="11" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="I999" t="s">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="K999" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="L999" t="s">
         <v>366</v>
@@ -69520,10 +69480,10 @@
         <v>82</v>
       </c>
       <c r="B1000" s="11" t="s">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="C1000" s="11" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="D1000" s="11" t="s">
         <v>366</v>
@@ -69538,7 +69498,7 @@
         <v>372</v>
       </c>
       <c r="I1000" t="s">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="K1000" t="s">
         <v>372</v>
@@ -69569,10 +69529,10 @@
         <v>82</v>
       </c>
       <c r="B1001" s="11" t="s">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="C1001" s="11" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="D1001" s="11" t="s">
         <v>366</v>
@@ -69587,7 +69547,7 @@
         <v>372</v>
       </c>
       <c r="I1001" t="s">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="K1001" t="s">
         <v>372</v>
@@ -69618,10 +69578,10 @@
         <v>82</v>
       </c>
       <c r="B1002" s="11" t="s">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C1002" s="11" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="D1002" s="11" t="s">
         <v>366</v>
@@ -69636,7 +69596,7 @@
         <v>372</v>
       </c>
       <c r="I1002" t="s">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="K1002" t="s">
         <v>372</v>
@@ -69667,10 +69627,10 @@
         <v>82</v>
       </c>
       <c r="B1003" s="11" t="s">
-        <v>2015</v>
+        <v>2013</v>
       </c>
       <c r="C1003" s="11" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="D1003" s="11" t="s">
         <v>366</v>
@@ -69685,7 +69645,7 @@
         <v>372</v>
       </c>
       <c r="I1003" t="s">
-        <v>2016</v>
+        <v>2014</v>
       </c>
       <c r="K1003" t="s">
         <v>372</v>
@@ -69716,34 +69676,34 @@
         <v>82</v>
       </c>
       <c r="B1004" s="11" t="s">
-        <v>2017</v>
+        <v>2015</v>
       </c>
       <c r="C1004" s="11" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="D1004" s="11" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="E1004" s="11" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="F1004" s="11" t="s">
-        <v>376</v>
+        <v>371</v>
       </c>
       <c r="G1004" s="11" t="s">
-        <v>79</v>
+        <v>372</v>
       </c>
       <c r="I1004" t="s">
-        <v>2018</v>
+        <v>2016</v>
       </c>
       <c r="K1004" t="s">
-        <v>80</v>
+        <v>372</v>
       </c>
       <c r="L1004" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="M1004" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="N1004" t="s">
         <v>2456</v>
@@ -69751,12 +69711,9 @@
       <c r="O1004" t="s">
         <v>2456</v>
       </c>
-      <c r="P1004" t="s">
-        <v>2259</v>
-      </c>
-      <c r="Q1004" t="e">
+      <c r="Q1004">
         <f t="shared" si="30"/>
-        <v>#N/A</v>
+        <v>1</v>
       </c>
       <c r="R1004">
         <f t="shared" si="31"/>
@@ -69768,10 +69725,10 @@
         <v>82</v>
       </c>
       <c r="B1005" s="11" t="s">
-        <v>2019</v>
+        <v>2017</v>
       </c>
       <c r="C1005" s="11" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="D1005" s="11" t="s">
         <v>374</v>
@@ -69786,7 +69743,7 @@
         <v>79</v>
       </c>
       <c r="I1005" t="s">
-        <v>2020</v>
+        <v>2018</v>
       </c>
       <c r="K1005" t="s">
         <v>80</v>
@@ -69820,10 +69777,10 @@
         <v>82</v>
       </c>
       <c r="B1006" s="11" t="s">
-        <v>2021</v>
+        <v>2019</v>
       </c>
       <c r="C1006" s="11" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="D1006" s="11" t="s">
         <v>374</v>
@@ -69838,7 +69795,7 @@
         <v>79</v>
       </c>
       <c r="I1006" t="s">
-        <v>2022</v>
+        <v>2020</v>
       </c>
       <c r="K1006" t="s">
         <v>80</v>
@@ -69872,10 +69829,10 @@
         <v>82</v>
       </c>
       <c r="B1007" s="11" t="s">
-        <v>2023</v>
+        <v>2021</v>
       </c>
       <c r="C1007" s="11" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="D1007" s="11" t="s">
         <v>374</v>
@@ -69890,7 +69847,7 @@
         <v>79</v>
       </c>
       <c r="I1007" t="s">
-        <v>2024</v>
+        <v>2022</v>
       </c>
       <c r="K1007" t="s">
         <v>80</v>
@@ -69924,10 +69881,10 @@
         <v>82</v>
       </c>
       <c r="B1008" s="11" t="s">
-        <v>2025</v>
+        <v>2023</v>
       </c>
       <c r="C1008" s="11" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="D1008" s="11" t="s">
         <v>374</v>
@@ -69942,7 +69899,7 @@
         <v>79</v>
       </c>
       <c r="I1008" t="s">
-        <v>2026</v>
+        <v>2024</v>
       </c>
       <c r="K1008" t="s">
         <v>80</v>
@@ -69976,10 +69933,10 @@
         <v>82</v>
       </c>
       <c r="B1009" s="11" t="s">
-        <v>2027</v>
+        <v>2025</v>
       </c>
       <c r="C1009" s="11" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="D1009" s="11" t="s">
         <v>374</v>
@@ -69994,7 +69951,7 @@
         <v>79</v>
       </c>
       <c r="I1009" t="s">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="K1009" t="s">
         <v>80</v>
@@ -70028,10 +69985,10 @@
         <v>82</v>
       </c>
       <c r="B1010" s="11" t="s">
-        <v>2029</v>
+        <v>2027</v>
       </c>
       <c r="C1010" s="11" t="s">
-        <v>79</v>
+        <v>2028</v>
       </c>
       <c r="D1010" s="11" t="s">
         <v>374</v>
@@ -70046,7 +70003,7 @@
         <v>79</v>
       </c>
       <c r="I1010" t="s">
-        <v>79</v>
+        <v>2028</v>
       </c>
       <c r="K1010" t="s">
         <v>80</v>
@@ -70080,10 +70037,10 @@
         <v>82</v>
       </c>
       <c r="B1011" s="11" t="s">
-        <v>2030</v>
+        <v>2029</v>
       </c>
       <c r="C1011" s="11" t="s">
-        <v>2031</v>
+        <v>79</v>
       </c>
       <c r="D1011" s="11" t="s">
         <v>374</v>
@@ -70098,7 +70055,7 @@
         <v>79</v>
       </c>
       <c r="I1011" t="s">
-        <v>2031</v>
+        <v>79</v>
       </c>
       <c r="K1011" t="s">
         <v>80</v>
@@ -70132,10 +70089,10 @@
         <v>82</v>
       </c>
       <c r="B1012" s="11" t="s">
-        <v>2032</v>
+        <v>2030</v>
       </c>
       <c r="C1012" s="11" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="D1012" s="11" t="s">
         <v>374</v>
@@ -70150,7 +70107,7 @@
         <v>79</v>
       </c>
       <c r="I1012" t="s">
-        <v>2033</v>
+        <v>2031</v>
       </c>
       <c r="K1012" t="s">
         <v>80</v>
@@ -70184,10 +70141,10 @@
         <v>82</v>
       </c>
       <c r="B1013" s="11" t="s">
-        <v>2034</v>
+        <v>2032</v>
       </c>
       <c r="C1013" s="11" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="D1013" s="11" t="s">
         <v>374</v>
@@ -70202,7 +70159,7 @@
         <v>79</v>
       </c>
       <c r="I1013" t="s">
-        <v>2035</v>
+        <v>2033</v>
       </c>
       <c r="K1013" t="s">
         <v>80</v>
@@ -70236,10 +70193,10 @@
         <v>82</v>
       </c>
       <c r="B1014" s="11" t="s">
-        <v>2036</v>
+        <v>2034</v>
       </c>
       <c r="C1014" s="11" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="D1014" s="11" t="s">
         <v>374</v>
@@ -70254,7 +70211,7 @@
         <v>79</v>
       </c>
       <c r="I1014" t="s">
-        <v>2037</v>
+        <v>2035</v>
       </c>
       <c r="K1014" t="s">
         <v>80</v>
@@ -70288,10 +70245,10 @@
         <v>82</v>
       </c>
       <c r="B1015" s="11" t="s">
-        <v>2038</v>
+        <v>2036</v>
       </c>
       <c r="C1015" s="11" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="D1015" s="11" t="s">
         <v>374</v>
@@ -70306,7 +70263,7 @@
         <v>79</v>
       </c>
       <c r="I1015" t="s">
-        <v>2039</v>
+        <v>2037</v>
       </c>
       <c r="K1015" t="s">
         <v>80</v>
@@ -70340,10 +70297,10 @@
         <v>82</v>
       </c>
       <c r="B1016" s="11" t="s">
-        <v>2040</v>
+        <v>2038</v>
       </c>
       <c r="C1016" s="11" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="D1016" s="11" t="s">
         <v>374</v>
@@ -70358,7 +70315,7 @@
         <v>79</v>
       </c>
       <c r="I1016" t="s">
-        <v>2041</v>
+        <v>2039</v>
       </c>
       <c r="K1016" t="s">
         <v>80</v>
@@ -70392,10 +70349,10 @@
         <v>82</v>
       </c>
       <c r="B1017" s="11" t="s">
-        <v>2042</v>
+        <v>2040</v>
       </c>
       <c r="C1017" s="11" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="D1017" s="11" t="s">
         <v>374</v>
@@ -70410,7 +70367,7 @@
         <v>79</v>
       </c>
       <c r="I1017" t="s">
-        <v>2043</v>
+        <v>2041</v>
       </c>
       <c r="K1017" t="s">
         <v>80</v>
@@ -70444,10 +70401,10 @@
         <v>82</v>
       </c>
       <c r="B1018" s="11" t="s">
-        <v>2044</v>
+        <v>2042</v>
       </c>
       <c r="C1018" s="11" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="D1018" s="11" t="s">
         <v>374</v>
@@ -70462,7 +70419,7 @@
         <v>79</v>
       </c>
       <c r="I1018" t="s">
-        <v>2045</v>
+        <v>2043</v>
       </c>
       <c r="K1018" t="s">
         <v>80</v>
@@ -70496,10 +70453,10 @@
         <v>82</v>
       </c>
       <c r="B1019" s="11" t="s">
-        <v>2046</v>
+        <v>2044</v>
       </c>
       <c r="C1019" s="11" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="D1019" s="11" t="s">
         <v>374</v>
@@ -70514,7 +70471,7 @@
         <v>79</v>
       </c>
       <c r="I1019" t="s">
-        <v>2047</v>
+        <v>2045</v>
       </c>
       <c r="K1019" t="s">
         <v>80</v>
@@ -70548,10 +70505,10 @@
         <v>82</v>
       </c>
       <c r="B1020" s="11" t="s">
-        <v>2048</v>
+        <v>2046</v>
       </c>
       <c r="C1020" s="11" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="D1020" s="11" t="s">
         <v>374</v>
@@ -70566,7 +70523,7 @@
         <v>79</v>
       </c>
       <c r="I1020" t="s">
-        <v>2049</v>
+        <v>2047</v>
       </c>
       <c r="K1020" t="s">
         <v>80</v>
@@ -70600,10 +70557,10 @@
         <v>82</v>
       </c>
       <c r="B1021" s="11" t="s">
-        <v>2050</v>
+        <v>2048</v>
       </c>
       <c r="C1021" s="11" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="D1021" s="11" t="s">
         <v>374</v>
@@ -70618,7 +70575,7 @@
         <v>79</v>
       </c>
       <c r="I1021" t="s">
-        <v>2051</v>
+        <v>2049</v>
       </c>
       <c r="K1021" t="s">
         <v>80</v>
@@ -70652,10 +70609,10 @@
         <v>82</v>
       </c>
       <c r="B1022" s="11" t="s">
-        <v>2052</v>
+        <v>2050</v>
       </c>
       <c r="C1022" s="11" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="D1022" s="11" t="s">
         <v>374</v>
@@ -70670,7 +70627,7 @@
         <v>79</v>
       </c>
       <c r="I1022" t="s">
-        <v>2053</v>
+        <v>2051</v>
       </c>
       <c r="K1022" t="s">
         <v>80</v>
@@ -70704,10 +70661,10 @@
         <v>82</v>
       </c>
       <c r="B1023" s="11" t="s">
-        <v>2054</v>
+        <v>2052</v>
       </c>
       <c r="C1023" s="11" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="D1023" s="11" t="s">
         <v>374</v>
@@ -70722,7 +70679,7 @@
         <v>79</v>
       </c>
       <c r="I1023" t="s">
-        <v>2055</v>
+        <v>2053</v>
       </c>
       <c r="K1023" t="s">
         <v>80</v>
@@ -70756,10 +70713,10 @@
         <v>82</v>
       </c>
       <c r="B1024" s="11" t="s">
-        <v>2056</v>
+        <v>2054</v>
       </c>
       <c r="C1024" s="11" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="D1024" s="11" t="s">
         <v>374</v>
@@ -70768,16 +70725,16 @@
         <v>375</v>
       </c>
       <c r="F1024" s="11" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="G1024" s="11" t="s">
-        <v>379</v>
+        <v>79</v>
       </c>
       <c r="I1024" t="s">
-        <v>2057</v>
+        <v>2055</v>
       </c>
       <c r="K1024" t="s">
-        <v>379</v>
+        <v>80</v>
       </c>
       <c r="L1024" t="s">
         <v>374</v>
@@ -70791,9 +70748,12 @@
       <c r="O1024" t="s">
         <v>2456</v>
       </c>
-      <c r="Q1024">
+      <c r="P1024" t="s">
+        <v>2259</v>
+      </c>
+      <c r="Q1024" t="e">
         <f t="shared" si="30"/>
-        <v>1</v>
+        <v>#N/A</v>
       </c>
       <c r="R1024">
         <f t="shared" si="31"/>
@@ -70805,10 +70765,10 @@
         <v>82</v>
       </c>
       <c r="B1025" s="11" t="s">
-        <v>2058</v>
+        <v>2056</v>
       </c>
       <c r="C1025" s="11" t="s">
-        <v>379</v>
+        <v>2057</v>
       </c>
       <c r="D1025" s="11" t="s">
         <v>374</v>
@@ -70823,7 +70783,7 @@
         <v>379</v>
       </c>
       <c r="I1025" t="s">
-        <v>379</v>
+        <v>2057</v>
       </c>
       <c r="K1025" t="s">
         <v>379</v>
@@ -70854,10 +70814,10 @@
         <v>82</v>
       </c>
       <c r="B1026" s="11" t="s">
-        <v>2059</v>
+        <v>2058</v>
       </c>
       <c r="C1026" s="11" t="s">
-        <v>2060</v>
+        <v>379</v>
       </c>
       <c r="D1026" s="11" t="s">
         <v>374</v>
@@ -70872,7 +70832,7 @@
         <v>379</v>
       </c>
       <c r="I1026" t="s">
-        <v>2060</v>
+        <v>379</v>
       </c>
       <c r="K1026" t="s">
         <v>379</v>
@@ -70903,10 +70863,10 @@
         <v>82</v>
       </c>
       <c r="B1027" s="11" t="s">
-        <v>2061</v>
+        <v>2059</v>
       </c>
       <c r="C1027" s="11" t="s">
-        <v>375</v>
+        <v>2060</v>
       </c>
       <c r="D1027" s="11" t="s">
         <v>374</v>
@@ -70921,7 +70881,7 @@
         <v>379</v>
       </c>
       <c r="I1027" t="s">
-        <v>375</v>
+        <v>2060</v>
       </c>
       <c r="K1027" t="s">
         <v>379</v>
@@ -70952,10 +70912,10 @@
         <v>82</v>
       </c>
       <c r="B1028" s="11" t="s">
-        <v>2062</v>
+        <v>2061</v>
       </c>
       <c r="C1028" s="11" t="s">
-        <v>2063</v>
+        <v>375</v>
       </c>
       <c r="D1028" s="11" t="s">
         <v>374</v>
@@ -70970,7 +70930,7 @@
         <v>379</v>
       </c>
       <c r="I1028" t="s">
-        <v>2063</v>
+        <v>375</v>
       </c>
       <c r="K1028" t="s">
         <v>379</v>
@@ -70988,11 +70948,11 @@
         <v>2456</v>
       </c>
       <c r="Q1028">
-        <f t="shared" ref="Q1028:Q1045" si="32">MATCH(G1028,K1028,0)</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="R1028">
-        <f t="shared" ref="R1028:R1045" si="33">MATCH(E1028,M1028,0)</f>
+        <f t="shared" si="31"/>
         <v>1</v>
       </c>
     </row>
@@ -71001,10 +70961,10 @@
         <v>82</v>
       </c>
       <c r="B1029" s="11" t="s">
-        <v>2064</v>
+        <v>2062</v>
       </c>
       <c r="C1029" s="11" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="D1029" s="11" t="s">
         <v>374</v>
@@ -71019,7 +70979,7 @@
         <v>379</v>
       </c>
       <c r="I1029" t="s">
-        <v>2065</v>
+        <v>2063</v>
       </c>
       <c r="K1029" t="s">
         <v>379</v>
@@ -71037,11 +70997,11 @@
         <v>2456</v>
       </c>
       <c r="Q1029">
-        <f t="shared" si="32"/>
+        <f t="shared" ref="Q1029:Q1046" si="32">MATCH(G1029,K1029,0)</f>
         <v>1</v>
       </c>
       <c r="R1029">
-        <f t="shared" si="33"/>
+        <f t="shared" ref="R1029:R1046" si="33">MATCH(E1029,M1029,0)</f>
         <v>1</v>
       </c>
     </row>
@@ -71050,10 +71010,10 @@
         <v>82</v>
       </c>
       <c r="B1030" s="11" t="s">
-        <v>2066</v>
+        <v>2064</v>
       </c>
       <c r="C1030" s="11" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="D1030" s="11" t="s">
         <v>374</v>
@@ -71068,7 +71028,7 @@
         <v>379</v>
       </c>
       <c r="I1030" t="s">
-        <v>2067</v>
+        <v>2065</v>
       </c>
       <c r="K1030" t="s">
         <v>379</v>
@@ -71099,10 +71059,10 @@
         <v>82</v>
       </c>
       <c r="B1031" s="11" t="s">
-        <v>2068</v>
+        <v>2066</v>
       </c>
       <c r="C1031" s="11" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="D1031" s="11" t="s">
         <v>374</v>
@@ -71117,7 +71077,7 @@
         <v>379</v>
       </c>
       <c r="I1031" t="s">
-        <v>2069</v>
+        <v>2067</v>
       </c>
       <c r="K1031" t="s">
         <v>379</v>
@@ -71148,10 +71108,10 @@
         <v>82</v>
       </c>
       <c r="B1032" s="11" t="s">
-        <v>2070</v>
+        <v>2068</v>
       </c>
       <c r="C1032" s="11" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="D1032" s="11" t="s">
         <v>374</v>
@@ -71166,7 +71126,7 @@
         <v>379</v>
       </c>
       <c r="I1032" t="s">
-        <v>2071</v>
+        <v>2069</v>
       </c>
       <c r="K1032" t="s">
         <v>379</v>
@@ -71197,10 +71157,10 @@
         <v>82</v>
       </c>
       <c r="B1033" s="11" t="s">
-        <v>2072</v>
+        <v>2070</v>
       </c>
       <c r="C1033" s="11" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="D1033" s="11" t="s">
         <v>374</v>
@@ -71215,7 +71175,7 @@
         <v>379</v>
       </c>
       <c r="I1033" t="s">
-        <v>2073</v>
+        <v>2071</v>
       </c>
       <c r="K1033" t="s">
         <v>379</v>
@@ -71246,10 +71206,10 @@
         <v>82</v>
       </c>
       <c r="B1034" s="11" t="s">
-        <v>2074</v>
+        <v>2072</v>
       </c>
       <c r="C1034" s="11" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="D1034" s="11" t="s">
         <v>374</v>
@@ -71264,7 +71224,7 @@
         <v>379</v>
       </c>
       <c r="I1034" t="s">
-        <v>2075</v>
+        <v>2073</v>
       </c>
       <c r="K1034" t="s">
         <v>379</v>
@@ -71295,10 +71255,10 @@
         <v>82</v>
       </c>
       <c r="B1035" s="11" t="s">
-        <v>2076</v>
+        <v>2074</v>
       </c>
       <c r="C1035" s="11" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="D1035" s="11" t="s">
         <v>374</v>
@@ -71313,7 +71273,7 @@
         <v>379</v>
       </c>
       <c r="I1035" t="s">
-        <v>2077</v>
+        <v>2075</v>
       </c>
       <c r="K1035" t="s">
         <v>379</v>
@@ -71344,10 +71304,10 @@
         <v>82</v>
       </c>
       <c r="B1036" s="11" t="s">
-        <v>2078</v>
+        <v>2076</v>
       </c>
       <c r="C1036" s="11" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="D1036" s="11" t="s">
         <v>374</v>
@@ -71362,7 +71322,7 @@
         <v>379</v>
       </c>
       <c r="I1036" t="s">
-        <v>2079</v>
+        <v>2077</v>
       </c>
       <c r="K1036" t="s">
         <v>379</v>
@@ -71393,10 +71353,10 @@
         <v>82</v>
       </c>
       <c r="B1037" s="11" t="s">
-        <v>2080</v>
+        <v>2078</v>
       </c>
       <c r="C1037" s="11" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="D1037" s="11" t="s">
         <v>374</v>
@@ -71411,7 +71371,7 @@
         <v>379</v>
       </c>
       <c r="I1037" t="s">
-        <v>2081</v>
+        <v>2079</v>
       </c>
       <c r="K1037" t="s">
         <v>379</v>
@@ -71442,10 +71402,10 @@
         <v>82</v>
       </c>
       <c r="B1038" s="11" t="s">
-        <v>2082</v>
+        <v>2080</v>
       </c>
       <c r="C1038" s="11" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="D1038" s="11" t="s">
         <v>374</v>
@@ -71460,7 +71420,7 @@
         <v>379</v>
       </c>
       <c r="I1038" t="s">
-        <v>2083</v>
+        <v>2081</v>
       </c>
       <c r="K1038" t="s">
         <v>379</v>
@@ -71491,10 +71451,10 @@
         <v>82</v>
       </c>
       <c r="B1039" s="11" t="s">
-        <v>2084</v>
+        <v>2082</v>
       </c>
       <c r="C1039" s="11" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="D1039" s="11" t="s">
         <v>374</v>
@@ -71509,7 +71469,7 @@
         <v>379</v>
       </c>
       <c r="I1039" t="s">
-        <v>2085</v>
+        <v>2083</v>
       </c>
       <c r="K1039" t="s">
         <v>379</v>
@@ -71540,10 +71500,10 @@
         <v>82</v>
       </c>
       <c r="B1040" s="11" t="s">
-        <v>2086</v>
+        <v>2084</v>
       </c>
       <c r="C1040" s="11" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
       <c r="D1040" s="11" t="s">
         <v>374</v>
@@ -71558,7 +71518,7 @@
         <v>379</v>
       </c>
       <c r="I1040" t="s">
-        <v>2087</v>
+        <v>2085</v>
       </c>
       <c r="K1040" t="s">
         <v>379</v>
@@ -71589,10 +71549,10 @@
         <v>82</v>
       </c>
       <c r="B1041" s="11" t="s">
-        <v>2088</v>
+        <v>2086</v>
       </c>
       <c r="C1041" s="11" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="D1041" s="11" t="s">
         <v>374</v>
@@ -71607,7 +71567,7 @@
         <v>379</v>
       </c>
       <c r="I1041" t="s">
-        <v>2089</v>
+        <v>2087</v>
       </c>
       <c r="K1041" t="s">
         <v>379</v>
@@ -71638,10 +71598,10 @@
         <v>82</v>
       </c>
       <c r="B1042" s="11" t="s">
-        <v>2090</v>
+        <v>2088</v>
       </c>
       <c r="C1042" s="11" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="D1042" s="11" t="s">
         <v>374</v>
@@ -71656,7 +71616,7 @@
         <v>379</v>
       </c>
       <c r="I1042" t="s">
-        <v>2091</v>
+        <v>2089</v>
       </c>
       <c r="K1042" t="s">
         <v>379</v>
@@ -71687,10 +71647,10 @@
         <v>82</v>
       </c>
       <c r="B1043" s="11" t="s">
-        <v>2092</v>
+        <v>2090</v>
       </c>
       <c r="C1043" s="11" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="D1043" s="11" t="s">
         <v>374</v>
@@ -71705,7 +71665,7 @@
         <v>379</v>
       </c>
       <c r="I1043" t="s">
-        <v>2093</v>
+        <v>2091</v>
       </c>
       <c r="K1043" t="s">
         <v>379</v>
@@ -71736,10 +71696,10 @@
         <v>82</v>
       </c>
       <c r="B1044" s="11" t="s">
-        <v>2094</v>
+        <v>2092</v>
       </c>
       <c r="C1044" s="11" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="D1044" s="11" t="s">
         <v>374</v>
@@ -71754,7 +71714,7 @@
         <v>379</v>
       </c>
       <c r="I1044" t="s">
-        <v>2095</v>
+        <v>2093</v>
       </c>
       <c r="K1044" t="s">
         <v>379</v>
@@ -71785,10 +71745,10 @@
         <v>82</v>
       </c>
       <c r="B1045" s="11" t="s">
-        <v>2096</v>
+        <v>2094</v>
       </c>
       <c r="C1045" s="11" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="D1045" s="11" t="s">
         <v>374</v>
@@ -71803,7 +71763,7 @@
         <v>379</v>
       </c>
       <c r="I1045" t="s">
-        <v>2097</v>
+        <v>2095</v>
       </c>
       <c r="K1045" t="s">
         <v>379</v>
@@ -71829,8 +71789,57 @@
         <v>1</v>
       </c>
     </row>
+    <row r="1046" spans="1:18" x14ac:dyDescent="0.35">
+      <c r="A1046" s="11" t="s">
+        <v>82</v>
+      </c>
+      <c r="B1046" s="11" t="s">
+        <v>2096</v>
+      </c>
+      <c r="C1046" s="11" t="s">
+        <v>2097</v>
+      </c>
+      <c r="D1046" s="11" t="s">
+        <v>374</v>
+      </c>
+      <c r="E1046" s="11" t="s">
+        <v>375</v>
+      </c>
+      <c r="F1046" s="11" t="s">
+        <v>378</v>
+      </c>
+      <c r="G1046" s="11" t="s">
+        <v>379</v>
+      </c>
+      <c r="I1046" t="s">
+        <v>2097</v>
+      </c>
+      <c r="K1046" t="s">
+        <v>379</v>
+      </c>
+      <c r="L1046" t="s">
+        <v>374</v>
+      </c>
+      <c r="M1046" t="s">
+        <v>375</v>
+      </c>
+      <c r="N1046" t="s">
+        <v>2456</v>
+      </c>
+      <c r="O1046" t="s">
+        <v>2456</v>
+      </c>
+      <c r="Q1046">
+        <f t="shared" si="32"/>
+        <v>1</v>
+      </c>
+      <c r="R1046">
+        <f t="shared" si="33"/>
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:R1045" xr:uid="{A48CAC62-0220-410E-AE02-62F4290F0D0F}"/>
+  <autoFilter ref="A1:R1046" xr:uid="{A48CAC62-0220-410E-AE02-62F4290F0D0F}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="I170:J170 I163:J167 I158:J158 I161:J161">
     <cfRule type="duplicateValues" dxfId="0" priority="16"/>
